--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.3/RANDOMSEARCH_DETAILS_C18.3.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.3/RANDOMSEARCH_DETAILS_C18.3.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.6935</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0985</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.6913</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0983</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.8618</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1098</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.8367</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1082</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8224</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.8688</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.7029</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7645</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1034</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.6692</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.7639</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.7668</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8995</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8995</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.7687</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9093</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.7695</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.7664</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.7662</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9569</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.6804</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0975</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.6502</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0953</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9656</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.6411</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0953</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.6555</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.6485</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9758</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.6539</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0956</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.6747</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.6848</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0978</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9577</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.6538</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0956</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9547</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.6581</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0959</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9123</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.6591</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.096</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9306</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.6582</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0959</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.6493</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0953</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.7089</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.7057</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0993</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9442</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.7003</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0989</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9353</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.6989</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0984</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9574</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.6933</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0984</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0985</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.7097</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.7058</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0993</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9451000000000001</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.6977</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.6975</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0987</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9185</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.6995</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0989</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9324</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.6973</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0987</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9554</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.6862</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0979</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.0989</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.7033</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0992</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.7764</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1042</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8642</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.7975</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1056</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.8028</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1059</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9424</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.7937</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1053</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8677</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.8183</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9529</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.7452</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1021</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.7568</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1029</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.7749</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1041</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8228</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.8682</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1102</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.8683</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1102</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8212</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.8699</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1103</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8228</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.8687</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1102</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8603</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.7936</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1053</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.7961</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1055</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8551</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.7894</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8811</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.7795</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.1044</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8788</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.1046</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.7642</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1034</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8806</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.7674</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1036</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.7167</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9528</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.7226</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1005</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8852</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.7271</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.1008</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.7185</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.1002</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.7129</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0998</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9397</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.7225</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.1005</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.1007</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.1007</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8264</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.8478</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.1089</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.8533</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1092</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8521</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.8497</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8516</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.8534</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.1092</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.1062</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.8544</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.8042</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9171</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.7266</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.1008</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9161</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.7272</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.1008</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9165</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.7294</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.101</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.6857</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0979</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.6867</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.098</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.6947</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0985</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.6694</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.6976</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.6975</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.0987</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.6947</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.0985</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.6975</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.0987</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.8618</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.1098</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.8259</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.8665</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.1101</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8962</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.8729</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.1105</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.8952</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.8729</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.1105</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.6912</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.0983</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9548</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.7248</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.1007</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9674</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.7004</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9607</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.7065</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.0994</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9406</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.6986</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0984</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.6852</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.0979</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9796</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.6908</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.0983</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9574</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.0985</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.7122</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0998</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.6882</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.6941</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.0985</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.6925</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.0984</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.7634</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8744</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.7686</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9406</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.6986</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.0988</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.6882</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9608</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.7736</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9608</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.7736</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9546</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.7032</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.6883</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.703</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9251</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.685</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0979</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.7104</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0997</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>C18.3</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.6975</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0987</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.3/RANDOMSEARCH_DETAILS_C18.3.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.3/RANDOMSEARCH_DETAILS_C18.3.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9388</v>
+        <v>0.9751</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6935</v>
+        <v>0.2776</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0527</v>
+        <v>0.0357</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0985</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9801</v>
+        <v>0.9808</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6913</v>
+        <v>0.2716</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0368</v>
+        <v>0.035</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0983</v>
+        <v>0.0988</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9104</v>
+        <v>0.8653</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8618</v>
+        <v>0.1379</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0585</v>
+        <v>0.0643</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1098</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8416</v>
+        <v>0.8196</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8367</v>
+        <v>0.1899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1082</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8224</v>
+        <v>0.8183</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8688</v>
+        <v>0.1783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0716</v>
+        <v>0.0706</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1102</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9114</v>
+        <v>0.893</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7029</v>
+        <v>0.2655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.055</v>
+        <v>0.059</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0992</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9126</v>
+        <v>0.8585</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7645</v>
+        <v>0.1788</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0575</v>
+        <v>0.0659</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1034</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9742</v>
+        <v>0.9631</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6692</v>
+        <v>0.2795</v>
       </c>
       <c r="G9" t="n">
-        <v>0.037</v>
+        <v>0.0436</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.8573</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7639</v>
+        <v>0.179</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0578</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1033</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9095</v>
+        <v>0.8568</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7668</v>
+        <v>0.1797</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0579</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1035</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8995</v>
+        <v>0.8563</v>
       </c>
       <c r="F12" t="n">
-        <v>1.771</v>
+        <v>0.1771</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0597</v>
+        <v>0.0663</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1038</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8995</v>
+        <v>0.8563</v>
       </c>
       <c r="F13" t="n">
-        <v>1.761</v>
+        <v>0.1778</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0596</v>
+        <v>0.0663</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1031</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.91</v>
+        <v>0.857</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7687</v>
+        <v>0.1799</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0579</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1037</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9093</v>
+        <v>0.8562</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7695</v>
+        <v>0.1767</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0582</v>
+        <v>0.0663</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1037</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.909</v>
+        <v>0.8426</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7664</v>
+        <v>0.1806</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0581</v>
+        <v>0.0688</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1035</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8999</v>
+        <v>0.8423</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7662</v>
+        <v>0.1782</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0596</v>
+        <v>0.0688</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1035</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9569</v>
+        <v>0.9739</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6804</v>
+        <v>0.2799</v>
       </c>
       <c r="G18" t="n">
-        <v>0.045</v>
+        <v>0.0361</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0975</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9581</v>
+        <v>0.9532</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6502</v>
+        <v>0.2974</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0435</v>
+        <v>0.0431</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0953</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9656</v>
+        <v>0.971</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6411</v>
+        <v>0.3102</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0398</v>
+        <v>0.0357</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0961</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9734</v>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>0.3025</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0505</v>
+        <v>0.0348</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0953</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9619</v>
+        <v>0.9516</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6555</v>
+        <v>0.3099</v>
       </c>
       <c r="G22" t="n">
-        <v>0.041</v>
+        <v>0.0441</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0961</v>
       </c>
     </row>
     <row r="23">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9762</v>
+        <v>0.9272</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6485</v>
+        <v>0.3239</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0359</v>
+        <v>0.051</v>
       </c>
       <c r="H23" t="n">
         <v>0.09520000000000001</v>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9758</v>
+        <v>0.9718</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6539</v>
+        <v>0.3178</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0347</v>
+        <v>0.0353</v>
       </c>
       <c r="H24" t="n">
         <v>0.0956</v>
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9736</v>
+        <v>0.9518</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6591</v>
+        <v>0.3202</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0354</v>
+        <v>0.044</v>
       </c>
       <c r="H25" t="n">
-        <v>0.096</v>
+        <v>0.0954</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.976</v>
+        <v>0.9734</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6747</v>
+        <v>0.2796</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.956</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6848</v>
+        <v>0.2783</v>
       </c>
       <c r="G27" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0978</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9577</v>
+        <v>0.9755</v>
       </c>
       <c r="F28" t="n">
-        <v>1.668</v>
+        <v>0.3095</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0442</v>
+        <v>0.0357</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9345</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6538</v>
+        <v>0.2873</v>
       </c>
       <c r="G29" t="n">
-        <v>0.044</v>
+        <v>0.0499</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0956</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9547</v>
+        <v>0.9559</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6581</v>
+        <v>0.3117</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0443</v>
+        <v>0.0434</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0959</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9123</v>
+        <v>0.9732</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6591</v>
+        <v>0.2958</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0569</v>
+        <v>0.035</v>
       </c>
       <c r="H31" t="n">
-        <v>0.096</v>
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9306</v>
+        <v>0.9262</v>
       </c>
       <c r="F32" t="n">
-        <v>1.6582</v>
+        <v>0.3039</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0512</v>
+        <v>0.0515</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0959</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9536</v>
+        <v>0.9422</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6493</v>
+        <v>0.3072</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0447</v>
+        <v>0.0471</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0953</v>
+        <v>0.0963</v>
       </c>
     </row>
     <row r="34">
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9827</v>
+        <v>0.9829</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7089</v>
+        <v>0.2429</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0367</v>
+        <v>0.0355</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.1007</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9643</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>1.7057</v>
+        <v>0.2564</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0445</v>
+        <v>0.0498</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0993</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9442</v>
+        <v>0.9666</v>
       </c>
       <c r="F36" t="n">
-        <v>1.7003</v>
+        <v>0.265</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0512</v>
+        <v>0.0433</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0989</v>
+        <v>0.0992</v>
       </c>
     </row>
     <row r="37">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9353</v>
+        <v>0.9355</v>
       </c>
       <c r="F37" t="n">
-        <v>1.6989</v>
+        <v>0.2767</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0535</v>
+        <v>0.0525</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0988</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9364</v>
+        <v>0.9583</v>
       </c>
       <c r="F38" t="n">
-        <v>1.693</v>
+        <v>0.2804</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0531</v>
+        <v>0.0434</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0984</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9574</v>
+        <v>0.9729</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6933</v>
+        <v>0.2918</v>
       </c>
       <c r="G39" t="n">
-        <v>0.045</v>
+        <v>0.0358</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0984</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9565</v>
+        <v>0.9166</v>
       </c>
       <c r="F40" t="n">
-        <v>1.694</v>
+        <v>0.2955</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0448</v>
+        <v>0.055</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0985</v>
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9826</v>
+        <v>0.983</v>
       </c>
       <c r="F41" t="n">
-        <v>1.7097</v>
+        <v>0.2447</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0366</v>
+        <v>0.0356</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9643</v>
+        <v>0.9524</v>
       </c>
       <c r="F42" t="n">
-        <v>1.7058</v>
+        <v>0.2526</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0446</v>
+        <v>0.05</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0993</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9671</v>
       </c>
       <c r="F43" t="n">
-        <v>1.6977</v>
+        <v>0.268</v>
       </c>
       <c r="G43" t="n">
-        <v>0.051</v>
+        <v>0.0431</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0988</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="44">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9367</v>
+        <v>0.9353</v>
       </c>
       <c r="F44" t="n">
-        <v>1.6975</v>
+        <v>0.2828</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0534</v>
+        <v>0.0525</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0987</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9185</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1.6995</v>
+        <v>0.277</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0566</v>
+        <v>0.0397</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0989</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9324</v>
+        <v>0.955</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6973</v>
+        <v>0.2831</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0535</v>
+        <v>0.044</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0987</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9554</v>
+        <v>0.9291</v>
       </c>
       <c r="F47" t="n">
-        <v>1.6862</v>
+        <v>0.2986</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0452</v>
+        <v>0.0525</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0979</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9715</v>
+        <v>0.946</v>
       </c>
       <c r="F48" t="n">
-        <v>1.699</v>
+        <v>0.2724</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0411</v>
+        <v>0.048</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0989</v>
+        <v>0.0987</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.928</v>
+        <v>0.9248</v>
       </c>
       <c r="F49" t="n">
-        <v>1.7033</v>
+        <v>0.2891</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0568</v>
+        <v>0.0561</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0992</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.8909</v>
+        <v>0.9413</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7764</v>
+        <v>0.2124</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0626</v>
+        <v>0.0495</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1042</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8642</v>
+        <v>0.9356</v>
       </c>
       <c r="F51" t="n">
-        <v>1.7975</v>
+        <v>0.1859</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0659</v>
+        <v>0.05</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1056</v>
+        <v>0.1044</v>
       </c>
     </row>
     <row r="52">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.861</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8028</v>
+        <v>0.1932</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0663</v>
+        <v>0.0655</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1059</v>
+        <v>0.1039</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9424</v>
+        <v>0.8968</v>
       </c>
       <c r="F53" t="n">
-        <v>1.7937</v>
+        <v>0.1957</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0501</v>
+        <v>0.0608</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1053</v>
+        <v>0.1038</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8677</v>
+        <v>0.9435</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8183</v>
+        <v>0.173</v>
       </c>
       <c r="G54" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0489</v>
       </c>
       <c r="H54" t="n">
-        <v>0.107</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9529</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>1.7452</v>
+        <v>0.2287</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0469</v>
+        <v>0.0376</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1021</v>
+        <v>0.1016</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>1.7568</v>
+        <v>0.2023</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0389</v>
+        <v>0.0455</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1029</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.881</v>
+        <v>0.9371</v>
       </c>
       <c r="F57" t="n">
-        <v>1.7749</v>
+        <v>0.1942</v>
       </c>
       <c r="G57" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0526</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1041</v>
+        <v>0.1039</v>
       </c>
     </row>
     <row r="58">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8228</v>
+        <v>0.8196</v>
       </c>
       <c r="F58" t="n">
-        <v>1.8682</v>
+        <v>0.176</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0716</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1102</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8219</v>
+        <v>0.819</v>
       </c>
       <c r="F59" t="n">
-        <v>1.8683</v>
+        <v>0.1785</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0717</v>
+        <v>0.0706</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1102</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="60">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8212</v>
+        <v>0.8192</v>
       </c>
       <c r="F60" t="n">
-        <v>1.8699</v>
+        <v>0.1769</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0718</v>
+        <v>0.0706</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1103</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="61">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8228</v>
+        <v>0.8195</v>
       </c>
       <c r="F61" t="n">
-        <v>1.8687</v>
+        <v>0.1768</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0717</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1102</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8603</v>
+        <v>0.8915</v>
       </c>
       <c r="F62" t="n">
-        <v>1.7936</v>
+        <v>0.1959</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0674</v>
+        <v>0.0603</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1053</v>
+        <v>0.1038</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8566</v>
+        <v>0.8903</v>
       </c>
       <c r="F63" t="n">
-        <v>1.7961</v>
+        <v>0.1824</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0677</v>
+        <v>0.0607</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1055</v>
+        <v>0.1046</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8551</v>
+        <v>0.9045</v>
       </c>
       <c r="F64" t="n">
-        <v>1.7894</v>
+        <v>0.197</v>
       </c>
       <c r="G64" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="H64" t="n">
-        <v>0.105</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8811</v>
+        <v>0.8851</v>
       </c>
       <c r="F65" t="n">
-        <v>1.7795</v>
+        <v>0.1916</v>
       </c>
       <c r="G65" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0608</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1044</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8788</v>
+        <v>0.9721</v>
       </c>
       <c r="F66" t="n">
-        <v>1.783</v>
+        <v>0.2041</v>
       </c>
       <c r="G66" t="n">
-        <v>0.066</v>
+        <v>0.0387</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1046</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8934</v>
+        <v>0.9332</v>
       </c>
       <c r="F67" t="n">
-        <v>1.7642</v>
+        <v>0.1968</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0626</v>
+        <v>0.0526</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1034</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8806</v>
+        <v>0.9727</v>
       </c>
       <c r="F68" t="n">
-        <v>1.7674</v>
+        <v>0.212</v>
       </c>
       <c r="G68" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0385</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1036</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9539</v>
+        <v>0.9505</v>
       </c>
       <c r="F69" t="n">
-        <v>1.7167</v>
+        <v>0.2998</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0461</v>
+        <v>0.0444</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1001</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9528</v>
+        <v>0.882</v>
       </c>
       <c r="F70" t="n">
-        <v>1.7226</v>
+        <v>0.2994</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0459</v>
+        <v>0.062</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1005</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="71">
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8852</v>
+        <v>0.8847</v>
       </c>
       <c r="F71" t="n">
-        <v>1.7271</v>
+        <v>0.2884</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0631</v>
+        <v>0.0619</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1008</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.956</v>
       </c>
       <c r="F72" t="n">
-        <v>1.7185</v>
+        <v>0.3089</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0548</v>
+        <v>0.043</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1002</v>
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9671</v>
       </c>
       <c r="F73" t="n">
-        <v>1.7129</v>
+        <v>0.2728</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0414</v>
+        <v>0.0433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0998</v>
+        <v>0.0987</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9397</v>
+        <v>0.9562</v>
       </c>
       <c r="F74" t="n">
-        <v>1.7225</v>
+        <v>0.2792</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0512</v>
+        <v>0.0435</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1005</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.922</v>
+        <v>0.8833</v>
       </c>
       <c r="F75" t="n">
-        <v>1.726</v>
+        <v>0.2526</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0543</v>
+        <v>0.0605</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1007</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.922</v>
+        <v>0.8833</v>
       </c>
       <c r="F76" t="n">
-        <v>1.726</v>
+        <v>0.2526</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0543</v>
+        <v>0.0605</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1007</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="77">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8264</v>
+        <v>0.8158</v>
       </c>
       <c r="F77" t="n">
-        <v>1.8478</v>
+        <v>0.1407</v>
       </c>
       <c r="G77" t="n">
         <v>0.07099999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1089</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8519</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>1.8533</v>
+        <v>0.1385</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0665</v>
+        <v>0.0709</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1092</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8521</v>
+        <v>0.8167</v>
       </c>
       <c r="F79" t="n">
-        <v>1.8497</v>
+        <v>0.1384</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0664</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0.109</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8516</v>
+        <v>0.8167</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8534</v>
+        <v>0.1384</v>
       </c>
       <c r="G80" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1092</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8599</v>
+        <v>0.89</v>
       </c>
       <c r="F81" t="n">
-        <v>1.807</v>
+        <v>0.1748</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0677</v>
+        <v>0.0606</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1062</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="82">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8544</v>
+        <v>0.853</v>
       </c>
       <c r="F82" t="n">
-        <v>1.8042</v>
+        <v>0.1655</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0682</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.106</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9171</v>
+        <v>0.9015</v>
       </c>
       <c r="F83" t="n">
-        <v>1.7266</v>
+        <v>0.2507</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0554</v>
+        <v>0.0563</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1008</v>
+        <v>0.1002</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9161</v>
+        <v>0.9125</v>
       </c>
       <c r="F84" t="n">
-        <v>1.7272</v>
+        <v>0.2537</v>
       </c>
       <c r="G84" t="n">
-        <v>0.055</v>
+        <v>0.0532</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1008</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9165</v>
+        <v>0.9016</v>
       </c>
       <c r="F85" t="n">
-        <v>1.7294</v>
+        <v>0.2499</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0554</v>
+        <v>0.0562</v>
       </c>
       <c r="H85" t="n">
-        <v>0.101</v>
+        <v>0.1002</v>
       </c>
     </row>
     <row r="86">
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9594</v>
+        <v>0.9587</v>
       </c>
       <c r="F86" t="n">
-        <v>1.6857</v>
+        <v>0.2783</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0447</v>
+        <v>0.0435</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0979</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="87">
@@ -3194,17 +3194,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9746</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>1.6867</v>
+        <v>0.2823</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0362</v>
+        <v>0.0439</v>
       </c>
       <c r="H87" t="n">
         <v>0.098</v>
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9666</v>
+        <v>0.9322</v>
       </c>
       <c r="F88" t="n">
-        <v>1.6947</v>
+        <v>0.278</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0412</v>
+        <v>0.0521</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0985</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.975</v>
+        <v>0.9573</v>
       </c>
       <c r="F89" t="n">
-        <v>1.6694</v>
+        <v>0.3072</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0365</v>
+        <v>0.0429</v>
       </c>
       <c r="H89" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0963</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.945</v>
+        <v>0.9671</v>
       </c>
       <c r="F90" t="n">
-        <v>1.6976</v>
+        <v>0.2679</v>
       </c>
       <c r="G90" t="n">
-        <v>0.051</v>
+        <v>0.0431</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0988</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="91">
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9367</v>
+        <v>0.9354</v>
       </c>
       <c r="F91" t="n">
-        <v>1.6975</v>
+        <v>0.2828</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0534</v>
+        <v>0.0525</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0987</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9666</v>
+        <v>0.9322</v>
       </c>
       <c r="F92" t="n">
-        <v>1.6947</v>
+        <v>0.278</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0412</v>
+        <v>0.0521</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0985</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="93">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9367</v>
+        <v>0.9354</v>
       </c>
       <c r="F93" t="n">
-        <v>1.6975</v>
+        <v>0.2828</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0534</v>
+        <v>0.0525</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0987</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9104</v>
+        <v>0.8653</v>
       </c>
       <c r="F94" t="n">
-        <v>1.8618</v>
+        <v>0.1379</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0585</v>
+        <v>0.0643</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1098</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8259</v>
+        <v>0.7876</v>
       </c>
       <c r="F95" t="n">
-        <v>1.8665</v>
+        <v>0.1036</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0718</v>
+        <v>0.0761</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1101</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8962</v>
+        <v>0.8636</v>
       </c>
       <c r="F96" t="n">
-        <v>1.8729</v>
+        <v>0.1409</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0607</v>
+        <v>0.0644</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1105</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8952</v>
+        <v>0.8636</v>
       </c>
       <c r="F97" t="n">
-        <v>1.8729</v>
+        <v>0.1431</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0614</v>
+        <v>0.0644</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1105</v>
+        <v>0.1071</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9762</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>1.6958</v>
+        <v>0.2622</v>
       </c>
       <c r="G98" t="n">
         <v>0.0372</v>
       </c>
       <c r="H98" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9739</v>
       </c>
       <c r="F99" t="n">
-        <v>1.6912</v>
+        <v>0.3036</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0495</v>
+        <v>0.0359</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0983</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9548</v>
+        <v>0.965</v>
       </c>
       <c r="F100" t="n">
-        <v>1.696</v>
+        <v>0.3002</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0457</v>
+        <v>0.0404</v>
       </c>
       <c r="H100" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9747</v>
+        <v>0.9571</v>
       </c>
       <c r="F101" t="n">
-        <v>1.71</v>
+        <v>0.2862</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0363</v>
+        <v>0.0431</v>
       </c>
       <c r="H101" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9749</v>
+        <v>0.9506</v>
       </c>
       <c r="F102" t="n">
-        <v>1.7248</v>
+        <v>0.2833</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0368</v>
+        <v>0.0442</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1007</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9674</v>
+        <v>0.9764</v>
       </c>
       <c r="F103" t="n">
-        <v>1.7004</v>
+        <v>0.2536</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0419</v>
+        <v>0.0369</v>
       </c>
       <c r="H103" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="104">
@@ -3738,17 +3738,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9607</v>
+        <v>0.9575</v>
       </c>
       <c r="F104" t="n">
-        <v>1.7065</v>
+        <v>0.2617</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0448</v>
+        <v>0.0445</v>
       </c>
       <c r="H104" t="n">
         <v>0.0994</v>
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9406</v>
+        <v>0.975</v>
       </c>
       <c r="F105" t="n">
-        <v>1.6986</v>
+        <v>0.3054</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0504</v>
+        <v>0.0362</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0988</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9433</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>1.693</v>
+        <v>0.2981</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0494</v>
+        <v>0.0349</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0984</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9649</v>
+        <v>0.9756</v>
       </c>
       <c r="F107" t="n">
-        <v>1.6852</v>
+        <v>0.2973</v>
       </c>
       <c r="G107" t="n">
-        <v>0.042</v>
+        <v>0.0353</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0979</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9796</v>
+        <v>0.9759</v>
       </c>
       <c r="F108" t="n">
-        <v>1.71</v>
+        <v>0.2447</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0385</v>
+        <v>0.0406</v>
       </c>
       <c r="H108" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.966</v>
+        <v>0.981</v>
       </c>
       <c r="F109" t="n">
-        <v>1.6908</v>
+        <v>0.2574</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0454</v>
+        <v>0.0357</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0983</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9211</v>
+        <v>0.9453</v>
       </c>
       <c r="F110" t="n">
-        <v>1.695</v>
+        <v>0.2753</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0578</v>
+        <v>0.0479</v>
       </c>
       <c r="H110" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0985</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9574</v>
+        <v>0.9751</v>
       </c>
       <c r="F111" t="n">
-        <v>1.694</v>
+        <v>0.2779</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0454</v>
+        <v>0.0363</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0985</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9799</v>
+        <v>0.9758</v>
       </c>
       <c r="F112" t="n">
-        <v>1.7122</v>
+        <v>0.2379</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0384</v>
+        <v>0.0405</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0998</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9808</v>
       </c>
       <c r="F113" t="n">
-        <v>1.6882</v>
+        <v>0.2635</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0451</v>
+        <v>0.0356</v>
       </c>
       <c r="H113" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.918</v>
+        <v>0.9459</v>
       </c>
       <c r="F114" t="n">
-        <v>1.6941</v>
+        <v>0.2771</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0582</v>
+        <v>0.0478</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0985</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9565</v>
+        <v>0.9718</v>
       </c>
       <c r="F115" t="n">
-        <v>1.6925</v>
+        <v>0.2697</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0459</v>
+        <v>0.0363</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0984</v>
+        <v>0.0989</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8966</v>
       </c>
       <c r="F116" t="n">
-        <v>1.7634</v>
+        <v>0.2159</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0577</v>
+        <v>0.0583</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1033</v>
+        <v>0.1025</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8744</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>1.7686</v>
+        <v>0.2119</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0639</v>
+        <v>0.0535</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1037</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9406</v>
+        <v>0.975</v>
       </c>
       <c r="F118" t="n">
-        <v>1.6986</v>
+        <v>0.3054</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0504</v>
+        <v>0.0362</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0988</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9808</v>
       </c>
       <c r="F119" t="n">
-        <v>1.6882</v>
+        <v>0.2635</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0451</v>
+        <v>0.0356</v>
       </c>
       <c r="H119" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9608</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>1.7736</v>
+        <v>0.2579</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0426</v>
+        <v>0.0358</v>
       </c>
       <c r="H120" t="n">
-        <v>0.104</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9608</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>1.7736</v>
+        <v>0.2579</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0426</v>
+        <v>0.0358</v>
       </c>
       <c r="H121" t="n">
-        <v>0.104</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9546</v>
+        <v>0.9735</v>
       </c>
       <c r="F122" t="n">
-        <v>1.7032</v>
+        <v>0.2582</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0449</v>
+        <v>0.0371</v>
       </c>
       <c r="H122" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9809</v>
       </c>
       <c r="F123" t="n">
-        <v>1.6883</v>
+        <v>0.2635</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0452</v>
+        <v>0.0356</v>
       </c>
       <c r="H123" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9567</v>
+        <v>0.9232</v>
       </c>
       <c r="F124" t="n">
-        <v>1.703</v>
+        <v>0.2718</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0455</v>
+        <v>0.0569</v>
       </c>
       <c r="H124" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0988</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9251</v>
+        <v>0.9606</v>
       </c>
       <c r="F125" t="n">
-        <v>1.685</v>
+        <v>0.2866</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0551</v>
+        <v>0.043</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0979</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="126">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9818</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>1.7104</v>
+        <v>0.2573</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0366</v>
+        <v>0.0496</v>
       </c>
       <c r="H126" t="n">
         <v>0.0997</v>
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9502</v>
       </c>
       <c r="F127" t="n">
-        <v>1.6975</v>
+        <v>0.2807</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0517</v>
+        <v>0.0482</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0987</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
   </sheetData>
